--- a/report_forms/042_food_inventory_form--report_forms.xlsx
+++ b/report_forms/042_food_inventory_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>meat</t>
+          <t>seafood</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Seafood</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>seafood</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seafood</t>
+          <t>Dessert</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>inventory_category_choices</t>
+          <t>inventory_subcategory_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>beef</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dessert</t>
+          <t>Beef</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>beef</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Beef</t>
+          <t>Chicken</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>chicken</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>pork</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Pork</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pork</t>
+          <t>lamb</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pork</t>
+          <t>Lamb</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lamb</t>
+          <t>turkey</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lamb</t>
+          <t>Turkey</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>turkey</t>
+          <t>veggie</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Veggie</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>veggie</t>
+          <t>seafood</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Veggie</t>
+          <t>Seafood</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>inventory_subcategory_choices</t>
+          <t>inventory_subcategory2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>seafood</t>
+          <t>beef</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seafood</t>
+          <t>Beef</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>beef</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Beef</t>
+          <t>Chicken</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>chicken</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>pork</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Pork</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>pork</t>
+          <t>lamb</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pork</t>
+          <t>Lamb</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lamb</t>
+          <t>turkey</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lamb</t>
+          <t>Turkey</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>turkey</t>
+          <t>veggie</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Veggie</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>veggie</t>
+          <t>seafood</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Veggie</t>
+          <t>Seafood</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>seafood</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seafood</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>inventory_subcategory2_choices</t>
+          <t>inventory_subcategory3_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>beef</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Beef</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>beef</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Beef</t>
+          <t>Chicken</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>chicken</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicken</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>pork</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Pork</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>pork</t>
+          <t>lamb</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pork</t>
+          <t>Lamb</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>lamb</t>
+          <t>turkey</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lamb</t>
+          <t>Turkey</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>turkey</t>
+          <t>veggie</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Veggie</t>
         </is>
       </c>
     </row>
@@ -1811,29 +1811,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>veggie</t>
+          <t>seafood</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Veggie</t>
+          <t>Seafood</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>inventory_subcategory3_choices</t>
+          <t>supplier_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>seafood</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seafood</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1845,27 +1845,10 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>supplier_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
